--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:20</t>
+    <t xml:space="preserve">2026-09-29 14:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:11</t>
+    <t xml:space="preserve">2026-09-29 18:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>54.74</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43.79</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="3">
@@ -521,10 +521,10 @@
         <v>7.37</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>41.63</v>
+        <v>41.62</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34.26</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="5">
@@ -535,10 +535,10 @@
         <v>3.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>41.27</v>
+        <v>41.26</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>37.82</v>
+        <v>37.83</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2024_maule_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:47</t>
+    <t xml:space="preserve">2026-10-05 04:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -496,7 +496,7 @@
         <v>54.74</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43.78</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>9.07</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>61.2</v>
+        <v>61.21</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>52.14</v>
@@ -521,10 +521,10 @@
         <v>7.37</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>41.62</v>
+        <v>41.63</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>34.25</v>
+        <v>34.26</v>
       </c>
     </row>
     <row r="5">
@@ -535,7 +535,7 @@
         <v>3.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>41.26</v>
+        <v>41.27</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>37.83</v>
